--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,709 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9936,0.0002,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.0002,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.2280,0.0001,0.0004,0.9367</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9948,0.0002,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.0002,0.9982</t>
+  </si>
+  <si>
+    <t>0.9973,0.0000,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0141,0.0002,0.0001,0.9966</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0034,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9719,0.0012,0.0137,0.0006</t>
+  </si>
+  <si>
+    <t>0.5638,0.0012,0.4928,0.0004</t>
+  </si>
+  <si>
+    <t>0.4097,0.0049,0.6057,0.0004</t>
+  </si>
+  <si>
+    <t>0.0957,0.0025,0.9018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9813,0.0020,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9974,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8512,0.0016,0.1331,0.0029</t>
+  </si>
+  <si>
+    <t>0.0579,0.0032,0.9291,0.0027</t>
+  </si>
+  <si>
+    <t>0.0134,0.0014,0.9848,0.0006</t>
+  </si>
+  <si>
+    <t>0.7061,0.0030,0.2732,0.0009</t>
+  </si>
+  <si>
+    <t>0.9315,0.0007,0.0791,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0014,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.9982,0.0007</t>
+  </si>
+  <si>
+    <t>0.4407,0.5797,0.0044,0.0005</t>
+  </si>
+  <si>
+    <t>0.9830,0.0033,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0042,0.9978,0.0010</t>
+  </si>
+  <si>
+    <t>0.0119,0.9737,0.0108,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9880,0.0023,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.0196,0.9851,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9983,0.0069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.6591,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0212,0.0329,0.9010,0.0132</t>
+  </si>
+  <si>
+    <t>0.0136,0.0122,0.9711,0.0013</t>
+  </si>
+  <si>
+    <t>0.3359,0.0005,0.7452,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0281,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9879,0.0092,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0019,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0186,0.0134,0.0002,0.9846</t>
+  </si>
+  <si>
+    <t>0.0001,0.9976,0.0010,0.0186</t>
+  </si>
+  <si>
+    <t>0.0003,0.9962,0.0380,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0051,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.3737,0.9469,0.0002</t>
+  </si>
+  <si>
+    <t>0.0569,0.0024,0.9547,0.0002</t>
+  </si>
+  <si>
+    <t>0.0103,0.0009,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0014,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0186,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0033,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0045,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.8049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0141,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0037,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9850,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9973,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.9983,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0006,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.8890,0.0311,0.0339,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9675,0.9829,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9796,0.7004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9977,0.0172,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.8500,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0002,0.0015,0.9955</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0004,0.9997</t>
+  </si>
+  <si>
+    <t>0.0033,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.9981,0.0721,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9957,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9707,0.9937,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9912,0.9067,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9726,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9168,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9985,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7796,0.0161,0.1403,0.0027</t>
-  </si>
-  <si>
-    <t>0.5055,0.0015,0.5321,0.0006</t>
-  </si>
-  <si>
-    <t>0.5509,0.0020,0.5070,0.0002</t>
-  </si>
-  <si>
-    <t>0.1148,0.0136,0.8179,0.0013</t>
-  </si>
-  <si>
-    <t>0.9823,0.0007,0.0086,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9959,0.0025,0.0002</t>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1689,0.0217,0.7441,0.0002</t>
+  </si>
+  <si>
+    <t>0.9905,0.0005,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0008,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9975,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.9957,0.0008,0.0003</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8169,0.0019,0.1869,0.0015</t>
-  </si>
-  <si>
-    <t>0.4709,0.0014,0.5474,0.0027</t>
-  </si>
-  <si>
-    <t>0.0069,0.0007,0.9920,0.0004</t>
-  </si>
-  <si>
-    <t>0.0164,0.0022,0.9819,0.0003</t>
-  </si>
-  <si>
-    <t>0.0646,0.0010,0.9587,0.0001</t>
-  </si>
-  <si>
-    <t>0.0165,0.0009,0.9858,0.0003</t>
-  </si>
-  <si>
-    <t>0.0137,0.0006,0.9917,0.0003</t>
-  </si>
-  <si>
-    <t>0.6153,0.3741,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.9670,0.0127,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0124,0.9983,0.0008</t>
-  </si>
-  <si>
-    <t>0.0599,0.9035,0.0152,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9860,0.0027,0.0044,0.0025</t>
-  </si>
-  <si>
-    <t>0.2732,0.8166,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.5747,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0058,0.0081,0.9863,0.0017</t>
-  </si>
-  <si>
-    <t>0.0017,0.1600,0.9669,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.0006,0.9963,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.6346,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9853,0.0194,0.0008</t>
-  </si>
-  <si>
-    <t>0.0024,0.0031,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0290,0.0003,0.9964</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9973,0.0070,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0065,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.8211,0.9828,0.0001</t>
-  </si>
-  <si>
-    <t>0.0401,0.0015,0.9664,0.0006</t>
-  </si>
-  <si>
-    <t>0.0079,0.0010,0.9927,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0051,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0018,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0050,0.0003,0.0001</t>
+    <t>0.9235,0.1522,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2850,0.0041,0.6725,0.0036</t>
+  </si>
+  <si>
+    <t>0.8580,0.0065,0.1050,0.0005</t>
+  </si>
+  <si>
+    <t>0.9344,0.0066,0.0265,0.0016</t>
+  </si>
+  <si>
+    <t>0.0885,0.0023,0.8943,0.0052</t>
+  </si>
+  <si>
+    <t>0.0024,0.0138,0.0044,0.9918</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.0002,0.0932</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7918,0.3383,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9450,0.0642,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.5968,0.9403,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9332,0.9769,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0239,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0019,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.9905,0.0003,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.7122,0.0142,0.2235,0.0034</t>
+  </si>
+  <si>
+    <t>0.9018,0.0003,0.1181,0.0005</t>
+  </si>
+  <si>
+    <t>0.8764,0.0308,0.0081,0.0027</t>
+  </si>
+  <si>
+    <t>0.0078,0.0000,0.0002,0.9979</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.9821,0.0000</t>
+  </si>
+  <si>
+    <t>0.0262,0.9779,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.1474,0.8781,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0005,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0127,0.9965,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0207,0.9704,0.0037,0.0015</t>
+  </si>
+  <si>
+    <t>0.9768,0.0057,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9681,0.0073,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.0739,0.9083,0.0044,0.0031</t>
+  </si>
+  <si>
+    <t>0.9836,0.0024,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.9697,0.0187,0.0019,0.0002</t>
   </si>
   <si>
     <t>0.9986,0.0002,0.0002,0.0002</t>
   </si>
   <si>
-    <t>0.9976,0.0007,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0036,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9306,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0142,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0028,0.9971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9910,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9906,0.0014,0.0018</t>
-  </si>
-  <si>
-    <t>0.0015,0.9980,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9440,0.0026,0.0529,0.0003</t>
-  </si>
-  <si>
-    <t>0.9073,0.0256,0.0279,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0028,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9595,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9785,0.7902,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0108,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9472,0.0000</t>
-  </si>
-  <si>
-    <t>0.0268,0.0000,0.0003,0.9927</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0005,0.9996</t>
-  </si>
-  <si>
-    <t>0.0179,0.0000,0.0000,0.9976</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9986,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9851,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9763,0.9860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9543,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.0019,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.9746,0.0014,0.0090,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9981,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9631,0.0719,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9401,0.0041,0.0312,0.0016</t>
-  </si>
-  <si>
-    <t>0.9346,0.0014,0.0562,0.0003</t>
-  </si>
-  <si>
-    <t>0.2821,0.0102,0.6598,0.0011</t>
-  </si>
-  <si>
-    <t>0.8793,0.0030,0.0919,0.0029</t>
-  </si>
-  <si>
-    <t>0.0039,0.0059,0.0016,0.9943</t>
-  </si>
-  <si>
-    <t>0.0004,0.9980,0.0088,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.0027,0.0065</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9856,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8506,0.1804,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.2856,0.7639,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0014,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9187,0.6297,0.0010</t>
-  </si>
-  <si>
-    <t>0.0007,0.6638,0.9613,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0061,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0012,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.9875,0.0005,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.5128,0.0079,0.4449,0.0052</t>
-  </si>
-  <si>
-    <t>0.9818,0.0002,0.0137,0.0001</t>
-  </si>
-  <si>
-    <t>0.9697,0.0010,0.0150,0.0008</t>
-  </si>
-  <si>
-    <t>0.0357,0.0002,0.0001,0.9935</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9958,0.8758,0.0000</t>
-  </si>
-  <si>
-    <t>0.4345,0.6774,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.5741,0.5131,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0022,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0219,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0002,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0138,0.9784,0.0013,0.0042</t>
-  </si>
-  <si>
-    <t>0.9882,0.0015,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9820,0.0028,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.0458,0.9403,0.0041,0.0026</t>
-  </si>
-  <si>
-    <t>0.9813,0.0031,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.7791,0.2125,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0018,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8359,0.1728,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.2886,0.7828,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.6051,0.4699,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0106,0.0827,0.9598,0.0005</t>
-  </si>
-  <si>
-    <t>0.8566,0.2012,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.8632,0.1247,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.8784,0.1044,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0055,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.9361,0.0294,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0087,0.9920,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0028,0.0323,0.9900,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0019,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0671,0.0036,0.9218,0.0010</t>
-  </si>
-  <si>
-    <t>0.0101,0.0015,0.9917,0.0001</t>
-  </si>
-  <si>
-    <t>0.2881,0.0196,0.6071,0.0036</t>
-  </si>
-  <si>
-    <t>0.5884,0.1103,0.1103,0.0005</t>
-  </si>
-  <si>
-    <t>0.3973,0.3617,0.0608,0.0004</t>
-  </si>
-  <si>
-    <t>0.9257,0.0147,0.0274,0.0003</t>
-  </si>
-  <si>
-    <t>0.9085,0.0130,0.0074,0.0047</t>
-  </si>
-  <si>
-    <t>0.0561,0.0195,0.8959,0.0009</t>
-  </si>
-  <si>
-    <t>0.9095,0.1522,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0461,0.9656,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0302,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9563,0.0732,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5276,0.6959,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9817,0.0055,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9627,0.0059,0.0117,0.0003</t>
-  </si>
-  <si>
-    <t>0.9727,0.0024,0.0041,0.0020</t>
-  </si>
-  <si>
-    <t>0.9294,0.0027,0.0544,0.0013</t>
-  </si>
-  <si>
-    <t>0.8441,0.0039,0.1725,0.0006</t>
-  </si>
-  <si>
-    <t>0.0047,0.0010,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.1316,0.9819,0.0005</t>
-  </si>
-  <si>
-    <t>0.0056,0.0269,0.9848,0.0002</t>
-  </si>
-  <si>
-    <t>0.0190,0.0172,0.9646,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.0468,0.9481,0.0010</t>
-  </si>
-  <si>
-    <t>0.9969,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0010,0.0001,0.0000</t>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8999,0.1050,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8557,0.1690,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.2586,0.8034,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9300,0.0483,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.9572,0.0637,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9697,0.0179,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5890,0.4755,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0065,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9034,0.0424,0.0012,0.0034</t>
+  </si>
+  <si>
+    <t>0.0005,0.0022,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0030,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0022,0.9943,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.1104,0.9655,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.0008,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0441,0.0014,0.9593,0.0006</t>
+  </si>
+  <si>
+    <t>0.0844,0.0023,0.9289,0.0002</t>
+  </si>
+  <si>
+    <t>0.0332,0.0055,0.9494,0.0051</t>
+  </si>
+  <si>
+    <t>0.5931,0.1891,0.0448,0.0005</t>
+  </si>
+  <si>
+    <t>0.1620,0.1895,0.3304,0.0007</t>
+  </si>
+  <si>
+    <t>0.9449,0.0067,0.0269,0.0005</t>
+  </si>
+  <si>
+    <t>0.9445,0.0042,0.0140,0.0038</t>
+  </si>
+  <si>
+    <t>0.3569,0.0414,0.3993,0.0031</t>
+  </si>
+  <si>
+    <t>0.7060,0.4519,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1171,0.9080,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.8894,0.2266,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9885,0.0220,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2898,0.8588,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9545,0.0220,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9901,0.0009,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9425,0.0041,0.0073,0.0070</t>
+  </si>
+  <si>
+    <t>0.9030,0.0044,0.0763,0.0014</t>
+  </si>
+  <si>
+    <t>0.5175,0.0019,0.5269,0.0007</t>
+  </si>
+  <si>
+    <t>0.0050,0.0005,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.1204,0.9697,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0774,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.0026,0.9884,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9105,0.3007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0014,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.0127,0.9935,0.0003</t>
+  </si>
+  <si>
+    <t>0.2134,0.6847,0.0381,0.0012</t>
+  </si>
+  <si>
+    <t>0.9798,0.0022,0.0061,0.0008</t>
+  </si>
+  <si>
+    <t>0.0961,0.0054,0.9089,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0243,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.7176,0.9505,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0023,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.1679,0.0026,0.8414,0.0014</t>
+  </si>
+  <si>
+    <t>0.9441,0.0018,0.0460,0.0006</t>
+  </si>
+  <si>
+    <t>0.8375,0.0010,0.1992,0.0014</t>
+  </si>
+  <si>
+    <t>0.9713,0.0008,0.0163,0.0011</t>
+  </si>
+  <si>
+    <t>0.9873,0.0107,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0011,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9986,0.0010,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0079,0.9922,0.0004</t>
-  </si>
-  <si>
-    <t>0.1180,0.0873,0.5905,0.0011</t>
-  </si>
-  <si>
-    <t>0.9681,0.0054,0.0100,0.0013</t>
-  </si>
-  <si>
-    <t>0.0024,0.0013,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0197,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9725,0.8171,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0061,0.0010,0.9917,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0046,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0036,0.9906,0.0007</t>
-  </si>
-  <si>
-    <t>0.9501,0.0005,0.0488,0.0007</t>
-  </si>
-  <si>
-    <t>0.6936,0.0005,0.4014,0.0017</t>
-  </si>
-  <si>
-    <t>0.9911,0.0002,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0027,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0095,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0025,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0137,0.9830,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0074,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0355,0.9961,0.0008</t>
-  </si>
-  <si>
-    <t>0.0219,0.0081,0.9587,0.0005</t>
-  </si>
-  <si>
-    <t>0.0045,0.0035,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0357,0.0011,0.9634,0.0021</t>
-  </si>
-  <si>
-    <t>0.5365,0.0020,0.5142,0.0005</t>
-  </si>
-  <si>
-    <t>0.0173,0.0033,0.9726,0.0018</t>
-  </si>
-  <si>
-    <t>0.9887,0.0001,0.0013,0.0052</t>
-  </si>
-  <si>
-    <t>0.0010,0.0193,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0187,0.0001,0.0034,0.9895</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.5118,0.0113,0.0008,0.3760</t>
+    <t>0.0030,0.0330,0.9694,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0077,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0234,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.0130,0.0122,0.9669,0.0008</t>
+  </si>
+  <si>
+    <t>0.0599,0.0006,0.9616,0.0004</t>
+  </si>
+  <si>
+    <t>0.3187,0.0012,0.7151,0.0024</t>
+  </si>
+  <si>
+    <t>0.0764,0.0044,0.9029,0.0027</t>
+  </si>
+  <si>
+    <t>0.0061,0.0028,0.9891,0.0010</t>
+  </si>
+  <si>
+    <t>0.9903,0.0002,0.0006,0.0036</t>
+  </si>
+  <si>
+    <t>0.0003,0.0145,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0601,0.0001,0.0007,0.9844</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.8966,0.0066,0.0007,0.0252</t>
   </si>
 </sst>
 </file>
@@ -1896,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1910,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1924,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1938,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1952,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1966,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1980,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1994,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2008,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2022,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2036,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2050,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2075,7 +2060,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2243,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2257,7 +2242,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2299,7 +2284,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2467,7 +2452,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2579,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2680,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2694,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2708,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2722,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2736,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2750,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2764,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2778,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2792,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2806,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2820,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2834,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2848,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2862,7 +2847,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2876,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2890,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2904,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2918,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2932,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2946,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2960,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2974,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2988,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3002,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3016,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3030,7 +3015,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3044,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3058,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3072,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3086,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3100,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3114,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3128,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3142,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3156,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3170,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3184,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3198,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3212,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3226,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3240,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3254,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3268,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3282,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3296,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3310,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3324,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3338,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3352,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3366,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3380,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3394,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3408,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3422,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3436,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3450,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3464,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3478,7 +3463,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3489,10 +3474,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3506,7 +3491,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3517,10 +3502,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,10 +3516,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3548,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3562,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3576,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3590,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3604,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3618,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3632,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3660,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3674,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>382</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3688,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>383</v>
+        <v>275</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3702,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3716,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>359</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3730,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3744,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3758,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>348</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3772,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3786,7 +3771,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3800,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3814,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3828,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3842,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3856,7 +3841,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3870,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3884,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3898,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3912,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3926,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3940,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3954,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3968,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3982,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3996,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4010,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4024,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4038,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4052,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4066,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4080,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4094,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4108,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4122,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4136,7 +4121,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4150,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4164,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4178,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>413</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4192,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>359</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4206,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4220,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>359</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4234,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4248,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4262,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4276,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>385</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4290,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4329,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4346,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4360,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4374,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4388,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4402,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4416,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4430,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4444,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4458,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4472,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4486,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4500,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4514,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4528,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4542,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4556,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4570,7 +4555,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,10 +4566,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4598,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4612,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4623,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4640,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4654,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4668,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4682,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4696,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4710,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4724,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4738,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4752,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4763,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4780,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4794,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4808,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4822,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4833,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4850,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4864,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4878,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4892,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>352</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4906,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4920,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4934,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4948,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>464</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4962,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4973,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4990,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5004,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5018,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5032,7 +5017,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5046,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5060,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5074,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5088,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5102,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5116,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5130,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5144,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5158,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5172,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5186,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5200,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5214,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5228,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5242,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5256,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5270,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5284,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5298,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5312,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5326,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5340,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5354,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5368,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5382,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5396,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5410,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5424,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5438,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>344</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5452,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
